--- a/backend/excel/notifications.xlsx
+++ b/backend/excel/notifications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7752,6 +7752,90 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ntf_ceed8c957145</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>emp_3dbe82c7aa1d</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>New lead assigned</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Lead "tcs" has been assigned to you.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:42:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ntf_3f46db7b2fa4</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>emp_20205e6cffa7</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>customer friendly</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:55:57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/excel/notifications.xlsx
+++ b/backend/excel/notifications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7836,6 +7836,750 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ntf_c43dac45d71d</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Project assigned</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>You are now managing project "Acme CRM Build".</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ntf_c3299182b2bb</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>dev_d502094df795</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Added to project</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>You have been assigned to project id prj_12311d0ebd08.</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ntf_6dbbe2b317a2</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Added to project team</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>You have been added to project "Acme CRM Build".</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ntf_5f026cf56206</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Added to project team</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>You have been added to project "Acme CRM Build".</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ntf_3beb23945841</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Added to project team</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>You have been added to project "Acme CRM Build".</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ntf_64792ab958f7</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Lead assigned</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Lead "Bob Buyer" is now assigned to you.</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ntf_3dbc3b6c14c3</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>New task assigned</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Task "Onboard client" in project "Acme CRM Build".</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ntf_e98a3a3b1110</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Lead assigned</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Lead "Bob Buyer" is now assigned to you.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ntf_8ef897b78a45</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>New lead assigned</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Lead "Second Buyer" has been assigned to you.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ntf_1adc837ea6d7</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>New lead assigned</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Lead "Jane Own Lead" has been assigned to you.</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ntf_0f15e05a9082</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>New lead assigned</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Lead "Dev Own Lead" has been assigned to you.</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ntf_531f25a8e3f8</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Follow-up reminder</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Call Bob today</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ntf_7904b2957421</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Re: Follow-up reminder</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Will do, thanks.</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>reply</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ntf_37a01376094b</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Message from the admin</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Dev question</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ntf_2b17714c5713</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Re: Message from the admin</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>On it.</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>reply</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>emp_24510a41c1f3</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ntf_b1c1994f5db3</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>New lead assigned</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Lead "Import One" has been assigned to you.</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ntf_b91d321a70a3</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>New lead assigned</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Lead "Import Two" has been assigned to you.</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ntf_111e29fef046</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>emp_ee9ef4d672db</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>New lead assigned</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Lead "Import Three" has been assigned to you.</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>emp_9370c1d0a3e4</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:59:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
